--- a/regulations/04.04.2025_C3_Example_V_Eloi.xlsx
+++ b/regulations/04.04.2025_C3_Example_V_Eloi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eloibernier/Documents/MS-ADS/2026_Spring/Capstone_I/Repo/Pyxidr-Capstone-Project/regulations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C61ECB9-3145-D24D-BFF9-799C16F91A86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A715F329-A24E-F940-86E6-E96064814C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-240" windowWidth="38400" windowHeight="21100" xr2:uid="{0223B9B8-7760-8B40-83A6-D3AD6AAA5CE0}"/>
+    <workbookView xWindow="1500" yWindow="1320" windowWidth="27640" windowHeight="16940" xr2:uid="{0223B9B8-7760-8B40-83A6-D3AD6AAA5CE0}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="1" r:id="rId1"/>
